--- a/artfynd/A 33350-2022 artfynd.xlsx
+++ b/artfynd/A 33350-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33350-2022 artfynd.xlsx
+++ b/artfynd/A 33350-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103307057</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614295.3748718284</v>
+        <v>614295</v>
       </c>
       <c r="R2" t="n">
-        <v>7223706.735090887</v>
+        <v>7223707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103307044</v>
+        <v>103307059</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614210.9795749304</v>
+        <v>614251</v>
       </c>
       <c r="R3" t="n">
-        <v>7223979.640866871</v>
+        <v>7223677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +859,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,37 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103307042</v>
+        <v>103307056</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614180.8763387424</v>
+        <v>614309</v>
       </c>
       <c r="R4" t="n">
-        <v>7223983.118104076</v>
+        <v>7223725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,19 +960,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103307056</v>
+        <v>103307042</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614309.0241790341</v>
+        <v>614181</v>
       </c>
       <c r="R5" t="n">
-        <v>7223724.970412832</v>
+        <v>7223983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1061,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103307059</v>
+        <v>103307044</v>
       </c>
       <c r="B6" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614250.5012289657</v>
+        <v>614211</v>
       </c>
       <c r="R6" t="n">
-        <v>7223677.176183945</v>
+        <v>7223980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,19 +1162,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,16 +1198,11 @@
         <v>103307046</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1310,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614395.9849841632</v>
+        <v>614396</v>
       </c>
       <c r="R7" t="n">
-        <v>7223888.965880129</v>
+        <v>7223889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,19 +1263,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,6 +1289,107 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103307054</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NV Lankasjön, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>614350</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7223705</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>

--- a/artfynd/A 33350-2022 artfynd.xlsx
+++ b/artfynd/A 33350-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103307057</v>
+        <v>135446275</v>
       </c>
       <c r="B2" t="n">
-        <v>90932</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NV Lankasjön, Storuman, Ly lm</t>
+          <t>Lankasjön, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614295</v>
+        <v>614291</v>
       </c>
       <c r="R2" t="n">
-        <v>7223707</v>
+        <v>7223712</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,50 +771,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103307057</t>
+          <t>https://artportalen.se/Sighting/135446275</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103307059</v>
+        <v>135446284</v>
       </c>
       <c r="B3" t="n">
-        <v>93222</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV Lankasjön, Storuman, Ly lm</t>
+          <t>Lankasjön, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614251</v>
+        <v>614377</v>
       </c>
       <c r="R3" t="n">
-        <v>7223677</v>
+        <v>7223889</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,31 +891,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103307059</t>
+          <t>https://artportalen.se/Sighting/135446284</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103307056</v>
+        <v>135446285</v>
       </c>
       <c r="B4" t="n">
-        <v>93189</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,37 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NV Lankasjön, Storuman, Ly lm</t>
+          <t>Lankasjön, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614309</v>
+        <v>614334</v>
       </c>
       <c r="R4" t="n">
-        <v>7223725</v>
+        <v>7223906</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,31 +1007,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103307056</t>
+          <t>https://artportalen.se/Sighting/135446285</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103307042</v>
+        <v>103307057</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614181</v>
+        <v>614295</v>
       </c>
       <c r="R5" t="n">
-        <v>7223983</v>
+        <v>7223707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,6 +1110,21 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1113,16 +1143,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103307042</t>
+          <t>https://artportalen.se/Sighting/103307057</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103307044</v>
+        <v>103307059</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>93222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1160,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614211</v>
+        <v>614251</v>
       </c>
       <c r="R6" t="n">
-        <v>7223980</v>
+        <v>7223677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,16 +1249,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103307044</t>
+          <t>https://artportalen.se/Sighting/103307059</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103307046</v>
+        <v>103307056</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614396</v>
+        <v>614309</v>
       </c>
       <c r="R7" t="n">
-        <v>7223889</v>
+        <v>7223725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,38 +1355,38 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103307046</t>
+          <t>https://artportalen.se/Sighting/103307056</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103307054</v>
+        <v>103307042</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614350</v>
+        <v>614181</v>
       </c>
       <c r="R8" t="n">
-        <v>7223705</v>
+        <v>7223983</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1461,454 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/103307042</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103307044</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NV Lankasjön, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>614211</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7223980</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307044</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103307046</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NV Lankasjön, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>614396</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7223889</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307046</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103307054</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NV Lankasjön, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>614350</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7223705</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/103307054</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135446279</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lankasjön, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>614255</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7223683</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tall som ringhackats i generationer. Gammalt i botten. Färskt högt upp.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446279</t>
         </is>
       </c>
     </row>
@@ -1444,6 +1921,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33350-2022 artfynd.xlsx
+++ b/artfynd/A 33350-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446275</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135446284</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135446285</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135446279</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
